--- a/docs/Literature_Review_Master.xlsx
+++ b/docs/Literature_Review_Master.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Multimodal Skin Lesion Classification Using Image and Clinical Metadata | Reconciled 2026-07-17: 3 (Project_Tracking.md) + 8 (user's Excel) + 8 (new, web-search-found) = 16 unique papers after duplicate resolution</t>
+          <t>Multimodal Skin Lesion Classification Using Image and Clinical Metadata | Reconciled 2026-07-17 (arithmetic corrected 2026-07-28): 3 (Project_Tracking.md) + 6 net-new (user's Excel, 8 rows minus 1 confirmed duplicate) + 7 (web-search-found) = 16 unique papers. Updated 2026-07-28: +3 targeted fairness-literature papers (rows 17-19) = 19 unique papers total (3+6+7+3=19).</t>
         </is>
       </c>
     </row>
@@ -1433,6 +1433,165 @@
       <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Directly parallels this thesis's own feature_whitelist.md exercise — strong comparison point for Methodology chapter</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Disparities in Dermatology AI Performance on a Diverse, Curated Clinical Image Set</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Daneshjou, Yekrang-Sis, Cai, et al. (Daneshjou senior/corresponding author)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NEW - found via targeted fairness-literature search 2026-07-28. Full text freely available (arXiv:2203.08807; published Science Advances). Date exception: published 2022, outside this project's preferred 2023-2025 window for the fairness search - included anyway because it is the field's foundational fairness-benchmark paper and the closest methodological analogue to this thesis's own Phase 8.3 Fitzpatrick fairness analysis (external, pathologically-confirmed test set built specifically to expose skin-tone performance gaps).</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DDI (Diverse Dermatology Images) - 656 images, pathologically confirmed diagnoses, curated for diverse Fitzpatrick skin-tone representation</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Quantify dermatology AI model and dermatologist performance disparities across skin tones and disease commonness</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Benchmarked existing SOTA dermatology classifiers (trained on standard datasets) against the newly curated, pathologically-confirmed DDI test set; separately compared dermatologist diagnostic performance across the same skin-tone/disease splits; also tested fine-tuning models on DDI itself</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>27-36 percentage-point ROC-AUC drop for SOTA models vs their originally reported test performance, concentrated on dark skin tones and uncommon diseases; dermatologists also perform worse on dark-skin/uncommon-disease images; fine-tuning on DDI narrows but does not eliminate the light/dark performance gap</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>DDI itself is relatively small (656 images); disparity demonstrated at the model-benchmark level, not root-caused to a single mechanism</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Direct methodological analogue to this thesis's Phase 8.3 Fitzpatrick fairness analysis - near-mandatory citation for framing our own fairness results and for situating this thesis's fairness contribution within the field's existing benchmark methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Skin Type Diversity in Skin Lesion Datasets: A Review</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Alipour, Burke &amp; Courtney</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NEW - found via targeted fairness-literature search 2026-07-28. Full text freely available (PMC11343783; Current Dermatology Reports; DOI 10.1007/s13671-024-00440-0).</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Systematic review across multiple public skin lesion datasets (not a single dataset)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Assess how frequently/completely public skin lesion datasets report Fitzpatrick skin type, and separately measure the actual skin-type diversity/representation within those datasets</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Reviews publicly available skin lesion datasets and their metadata; evaluates both whether skin type is reported at all and, independently, how diverse/representative that reporting actually is - explicitly notes that prior work does one or the other but not both together</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Review paper, no single quantitative headline metric; core finding is that under-representation of darker skin types is a systemic, field-wide dataset problem, not isolated to any one dataset or study</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Review-level (not a new dataset or model); scope limited to skin lesion datasets with publicly available metadata</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Strongest available citation for this thesis's 'Literature Gap: Fitzpatrick/Skin-Tone Fairness' section - independently confirms under-representation is systemic across the field, directly corroborating this thesis's own Phase 8.3 finding (PAD-UFES-20 test split: only 3 rows total across Fitzpatrick V/VI, 38% missing entirely)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>A Framework for Evaluating the Efficacy of Foundation Embedding Models in Healthcare</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Xu, Gui, Rotemberg, Wang, Chen &amp; Daneshjou</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NEW - found via targeted fairness-literature search 2026-07-28. Free preprint (medRxiv 2024.04.17.24305983, posted 2024-04-19).</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Google Health's Derm Foundation Model pretrained embeddings, evaluated on dermatology image classification tasks (not a new dataset)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Propose and pilot a 3-axis framework (general performance / bias-fairness / confounders) for evaluating medical foundation models, applied to dermatology</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Evaluates Derm Foundation Model embeddings plus general-purpose CLIP embeddings across the 3 proposed axes; measures per-Fitzpatrick-group sensitivity directly on the pretrained embedding space</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Foundation-model embeddings exceed SOTA classification accuracy; general-purpose CLIP embeddings are also informative for medical tasks; lower sensitivity found for darker Fitzpatrick tones (4-6), present even at the pretrained-embedding level before any task-specific fine-tuning; image quality also significantly affects performance</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Single foundation-model family evaluated in depth (Derm Foundation Model); the 3-axis framework is proposed/piloted, not yet an established field standard</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Confirms skin-tone-linked bias exists even inside pretrained foundation-model embeddings, not just end-task classifiers - relevant caution if this thesis's future work ever considers a foundation-model backbone. The paper's 3-axis evaluation framework (general performance / bias-fairness / confounders) is a citable structure for organizing this thesis's own Phase 8.3 write-up in the Discussion/Results chapter.</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1631,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>16 unique papers reconciled (target: 15-20+). Technically at target, but 8 of these (rows 10-16 minus one) are abstract-only — not yet full-text read.</t>
+          <t>19 unique papers reconciled (target: 15-20+). 3 fairness-focused papers added 2026-07-28 (rows 17-19) specifically to fill the previously-flagged Fitzpatrick/skin-tone fairness gap. Of the original 16, 8 rows (10-16 minus one) remain abstract-only - not yet full-text read; see docs/Literature_Review.md for current per-row full-text status.</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1703,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>NONE of the 16 papers above focus on Fitzpatrick/skin-tone fairness — yet this thesis's Phase 8 includes a dedicated fairness analysis. Actively search for 2-3 papers specifically on skin-tone bias in dermatology AI before Phase 9 writing begins; this is a citable gap this thesis's own fairness analysis will help fill.</t>
+          <t>RESOLVED 2026-07-28: rows 17-19 added specifically to address this gap - Daneshjou et al. 2022 (DDI dataset, quantifies dermatology AI performance disparity across Fitzpatrick skin tones, 27-36pp AUC drop on dark skin/uncommon disease), Alipour et al. 2024 (systematic review confirming under-representation of darker skin types is systemic across public dermatology datasets, not PAD-UFES-20-specific), Xu, Gui, Rotemberg, Wang, Chen &amp; Daneshjou 2024 (foundation-model fairness framework, finds skin-tone-linked bias even in pretrained embeddings). See docs/Literature_Review.md for full detail on all three.</t>
         </is>
       </c>
     </row>
